--- a/output/tabelas/3_2_despesa_por_funcao.xlsx
+++ b/output/tabelas/3_2_despesa_por_funcao.xlsx
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T21:36:28</t>
+          <t>2026-07-02T22:05:40</t>
         </is>
       </c>
     </row>
